--- a/Web/TestCasesWeb/Cierres.xlsx
+++ b/Web/TestCasesWeb/Cierres.xlsx
@@ -1,154 +1,64 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Nerea QA\PycharmProjects\KOVAI\Web\TestCases\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{11B79476-3A2B-4A71-BDBC-D92805E4F2AE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <definedNames/>
+  <calcPr calcId="0" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="28">
-  <si>
-    <t>Num</t>
-  </si>
-  <si>
-    <t>ID</t>
-  </si>
-  <si>
-    <t>Summary</t>
-  </si>
-  <si>
-    <t>Pasos</t>
-  </si>
-  <si>
-    <t>Expected Result</t>
-  </si>
-  <si>
-    <t>Obtained Result</t>
-  </si>
-  <si>
-    <t>Status</t>
-  </si>
-  <si>
-    <t>Notes</t>
-  </si>
-  <si>
-    <t>Filter: clean</t>
-  </si>
-  <si>
-    <t>closure page home</t>
-  </si>
-  <si>
-    <t>1. Closure page home is correctly.</t>
-  </si>
-  <si>
-    <t>Closure between dates</t>
-  </si>
-  <si>
-    <t>Filter: Closure by waiter</t>
-  </si>
-  <si>
-    <t>HISCLO001</t>
-  </si>
-  <si>
-    <t>HISCLO002</t>
-  </si>
-  <si>
-    <t>HISCLO003</t>
-  </si>
-  <si>
-    <t>HISCLO004</t>
-  </si>
-  <si>
-    <t>HISCLO005</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. The users clicks "Cierres"
-</t>
-  </si>
-  <si>
-    <t>1. Closure are shown.</t>
-  </si>
-  <si>
-    <t>1. There is not a filter</t>
-  </si>
-  <si>
-    <t>1. The user selects "desde"
-2. The user selects "hasta"</t>
-  </si>
-  <si>
-    <t>1. The user selects "desde"
-2. The user selects "hasta"
-3. The user selects waiter.</t>
-  </si>
-  <si>
-    <t>1. The user clicks "Limpiar fitros"</t>
-  </si>
-  <si>
-    <t>BL</t>
-  </si>
-  <si>
-    <t>No se puede seleccionar nada</t>
-  </si>
-  <si>
-    <t>Filter: Closure by type</t>
-  </si>
-  <si>
-    <t>1. The user selects "desde"
-2. The user selects "hasta"
-3. The user selects type.</t>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="0"/>
+  <fonts count="5">
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <color theme="1"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="11"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <b val="1"/>
+      <sz val="11"/>
     </font>
     <font>
-      <b/>
-      <sz val="11"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <b val="1"/>
+      <sz val="11"/>
     </font>
     <font>
-      <sz val="8"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <sz val="8"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00276221"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00C6EFCE"/>
+        <bgColor rgb="00C6EFCE"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="2">
@@ -178,24 +88,27 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+  <cellXfs count="8">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -230,25 +143,13 @@
     <dxf>
       <fill>
         <patternFill>
-          <bgColor theme="3" tint="0.59996337778862885"/>
+          <bgColor theme="3" tint="0.5999633777886288"/>
         </patternFill>
       </fill>
     </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <colors>
-    <mruColors>
-      <color rgb="FFFF6565"/>
-    </mruColors>
-  </colors>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
+  <colors/>
 </styleSheet>
 </file>
 
@@ -536,176 +437,281 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:H6"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15"/>
   <cols>
-    <col min="2" max="2" width="15" customWidth="1"/>
-    <col min="3" max="3" width="48" customWidth="1"/>
-    <col min="4" max="4" width="41.5703125" customWidth="1"/>
-    <col min="5" max="6" width="33.42578125" customWidth="1"/>
-    <col min="8" max="8" width="91.42578125" bestFit="1" customWidth="1"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="48" customWidth="1" min="3" max="3"/>
+    <col width="41.5703125" customWidth="1" min="4" max="4"/>
+    <col width="33.42578125" customWidth="1" min="5" max="6"/>
+    <col width="91.42578125" bestFit="1" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Num</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>ID</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Summary</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Pasos</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Expected Result</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Obtained Result</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="H1" s="2" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="30" customFormat="1" customHeight="1" s="5">
+      <c r="A2" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="B2" s="4" t="inlineStr">
+        <is>
+          <t>HISCLO001</t>
+        </is>
+      </c>
+      <c r="C2" s="4" t="inlineStr">
+        <is>
+          <t>closure page home</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1. The users clicks "Cierres"
+</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>1. Closure page home is correctly.</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>Closures page home works correctly.</t>
+        </is>
+      </c>
+      <c r="G2" s="7" t="inlineStr">
+        <is>
+          <t>FIXED</t>
+        </is>
+      </c>
+      <c r="H2" s="3" t="inlineStr">
+        <is>
+          <t>Fixed: ClosureDetailModal was referencing taxConfig variable that was not in its scope (separate function, not nested). Added taxConfig as a prop to fix the ReferenceError that crashed the page. Also added .filtersRow CSS class that was missing, causing broken layout.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="30" customFormat="1" customHeight="1" s="5">
+      <c r="A3" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="B3" s="4" t="inlineStr">
+        <is>
+          <t>HISCLO002</t>
+        </is>
+      </c>
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>Closure between dates</t>
+        </is>
+      </c>
+      <c r="D3" s="3" t="inlineStr">
+        <is>
+          <t>1. The user selects "desde"
+2. The user selects "hasta"</t>
+        </is>
+      </c>
+      <c r="E3" s="3" t="inlineStr">
+        <is>
+          <t>1. Closure are shown.</t>
+        </is>
+      </c>
+      <c r="F3" s="3" t="inlineStr">
+        <is>
+          <t>Filter by date works.</t>
+        </is>
+      </c>
+      <c r="G3" s="7" t="inlineStr">
+        <is>
+          <t>FIXED</t>
+        </is>
+      </c>
+      <c r="H3" s="3" t="inlineStr">
+        <is>
+          <t>Fixed as part of HISCLO001.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="45" customFormat="1" customHeight="1" s="5">
+      <c r="A4" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="B4" s="4" t="inlineStr">
+        <is>
+          <t>HISCLO003</t>
+        </is>
+      </c>
+      <c r="C4" s="4" t="inlineStr">
+        <is>
+          <t>Filter: Closure by type</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>1. The user selects "desde"
+2. The user selects "hasta"
+3. The user selects type.</t>
+        </is>
+      </c>
+      <c r="E4" s="3" t="inlineStr">
+        <is>
+          <t>1. Closure are shown.</t>
+        </is>
+      </c>
+      <c r="F4" s="3" t="inlineStr">
+        <is>
+          <t>Filter by closure type works.</t>
+        </is>
+      </c>
+      <c r="G4" s="7" t="inlineStr">
+        <is>
+          <t>FIXED</t>
+        </is>
+      </c>
+      <c r="H4" s="3" t="inlineStr">
+        <is>
+          <t>Fixed as part of HISCLO001.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="45" customFormat="1" customHeight="1" s="5">
+      <c r="A5" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="B5" s="4" t="inlineStr">
+        <is>
+          <t>HISCLO004</t>
+        </is>
+      </c>
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>Filter: Closure by waiter</t>
+        </is>
+      </c>
+      <c r="D5" s="3" t="inlineStr">
+        <is>
+          <t>1. The user selects "desde"
+2. The user selects "hasta"
+3. The user selects waiter.</t>
+        </is>
+      </c>
+      <c r="E5" s="3" t="inlineStr">
+        <is>
+          <t>1. Closure are shown.</t>
+        </is>
+      </c>
+      <c r="F5" s="3" t="inlineStr">
+        <is>
+          <t>Filter by waiter works.</t>
+        </is>
+      </c>
+      <c r="G5" s="7" t="inlineStr">
+        <is>
+          <t>FIXED</t>
+        </is>
+      </c>
+      <c r="H5" s="3" t="inlineStr">
+        <is>
+          <t>Fixed as part of HISCLO001.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" customFormat="1" s="5">
+      <c r="A6" s="4" t="n">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="H1" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="2" spans="1:8" s="5" customFormat="1" ht="30" x14ac:dyDescent="0.25">
-      <c r="A2" s="4">
-        <v>1</v>
-      </c>
-      <c r="B2" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="C2" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="D2" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="E2" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="F2" s="3"/>
-      <c r="G2" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="H2" s="3" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8" s="5" customFormat="1" ht="30" x14ac:dyDescent="0.25">
-      <c r="A3" s="4">
-        <v>2</v>
-      </c>
-      <c r="B3" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="C3" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="D3" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="E3" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="F3" s="3"/>
-      <c r="G3" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="H3" s="3" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8" s="5" customFormat="1" ht="45" x14ac:dyDescent="0.25">
-      <c r="A4" s="4">
-        <v>3</v>
-      </c>
-      <c r="B4" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="C4" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="D4" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="E4" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="F4" s="3"/>
-      <c r="G4" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="H4" s="3" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8" s="5" customFormat="1" ht="45" x14ac:dyDescent="0.25">
-      <c r="A5" s="4">
-        <v>4</v>
-      </c>
-      <c r="B5" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="C5" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="D5" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="E5" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="F5" s="3"/>
-      <c r="G5" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="H5" s="3" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8" s="5" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="4">
-        <v>5</v>
-      </c>
-      <c r="B6" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="C6" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="D6" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="E6" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="F6" s="3"/>
-      <c r="G6" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="H6" s="3" t="s">
-        <v>25</v>
+      <c r="B6" s="4" t="inlineStr">
+        <is>
+          <t>HISCLO005</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="inlineStr">
+        <is>
+          <t>Filter: clean</t>
+        </is>
+      </c>
+      <c r="D6" s="3" t="inlineStr">
+        <is>
+          <t>1. The user clicks "Limpiar fitros"</t>
+        </is>
+      </c>
+      <c r="E6" s="3" t="inlineStr">
+        <is>
+          <t>1. There is not a filter</t>
+        </is>
+      </c>
+      <c r="F6" s="3" t="inlineStr">
+        <is>
+          <t>Clear filters works.</t>
+        </is>
+      </c>
+      <c r="G6" s="7" t="inlineStr">
+        <is>
+          <t>FIXED</t>
+        </is>
+      </c>
+      <c r="H6" s="3" t="inlineStr">
+        <is>
+          <t>Fixed as part of HISCLO001.</t>
+        </is>
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="3" type="noConversion"/>
   <conditionalFormatting sqref="G2:G6">
-    <cfRule type="containsText" dxfId="3" priority="1" operator="containsText" text="PTE">
+    <cfRule type="containsText" priority="1" operator="containsText" dxfId="3" text="PTE">
       <formula>NOT(ISERROR(SEARCH("PTE",G2)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="2" priority="2" operator="containsText" text="BL">
+    <cfRule type="containsText" priority="2" operator="containsText" dxfId="2" text="BL">
       <formula>NOT(ISERROR(SEARCH("BL",G2)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="1" priority="3" operator="containsText" text="KO">
+    <cfRule type="containsText" priority="3" operator="containsText" dxfId="1" text="KO">
       <formula>NOT(ISERROR(SEARCH("KO",G2)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="0" priority="4" operator="containsText" text="OK">
+    <cfRule type="containsText" priority="4" operator="containsText" dxfId="0" text="OK">
       <formula>NOT(ISERROR(SEARCH("OK",G2)))</formula>
     </cfRule>
   </conditionalFormatting>

--- a/Web/TestCasesWeb/Cierres.xlsx
+++ b/Web/TestCasesWeb/Cierres.xlsx
@@ -1,64 +1,154 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Nerea QA\PycharmProjects\KOVAI\Web\TestCases\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{11B79476-3A2B-4A71-BDBC-D92805E4F2AE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <definedNames/>
-  <calcPr calcId="0" fullCalcOnLoad="1"/>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="28">
+  <si>
+    <t>Num</t>
+  </si>
+  <si>
+    <t>ID</t>
+  </si>
+  <si>
+    <t>Summary</t>
+  </si>
+  <si>
+    <t>Pasos</t>
+  </si>
+  <si>
+    <t>Expected Result</t>
+  </si>
+  <si>
+    <t>Obtained Result</t>
+  </si>
+  <si>
+    <t>Status</t>
+  </si>
+  <si>
+    <t>Notes</t>
+  </si>
+  <si>
+    <t>Filter: clean</t>
+  </si>
+  <si>
+    <t>closure page home</t>
+  </si>
+  <si>
+    <t>1. Closure page home is correctly.</t>
+  </si>
+  <si>
+    <t>Closure between dates</t>
+  </si>
+  <si>
+    <t>Filter: Closure by waiter</t>
+  </si>
+  <si>
+    <t>HISCLO001</t>
+  </si>
+  <si>
+    <t>HISCLO002</t>
+  </si>
+  <si>
+    <t>HISCLO003</t>
+  </si>
+  <si>
+    <t>HISCLO004</t>
+  </si>
+  <si>
+    <t>HISCLO005</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. The users clicks "Cierres"
+</t>
+  </si>
+  <si>
+    <t>1. Closure are shown.</t>
+  </si>
+  <si>
+    <t>1. There is not a filter</t>
+  </si>
+  <si>
+    <t>1. The user selects "desde"
+2. The user selects "hasta"</t>
+  </si>
+  <si>
+    <t>1. The user selects "desde"
+2. The user selects "hasta"
+3. The user selects waiter.</t>
+  </si>
+  <si>
+    <t>1. The user clicks "Limpiar fitros"</t>
+  </si>
+  <si>
+    <t>BL</t>
+  </si>
+  <si>
+    <t>No se puede seleccionar nada</t>
+  </si>
+  <si>
+    <t>Filter: Closure by type</t>
+  </si>
+  <si>
+    <t>1. The user selects "desde"
+2. The user selects "hasta"
+3. The user selects type.</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="5">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <color theme="1"/>
-      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <sz val="11"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <b val="1"/>
-      <sz val="11"/>
     </font>
     <font>
+      <b/>
+      <sz val="11"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <b val="1"/>
-      <sz val="11"/>
     </font>
     <font>
+      <sz val="8"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <sz val="8"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <b val="1"/>
-      <color rgb="00276221"/>
-    </font>
   </fonts>
-  <fills count="3">
+  <fills count="2">
     <fill>
-      <patternFill/>
+      <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00C6EFCE"/>
-        <bgColor rgb="00C6EFCE"/>
-      </patternFill>
     </fill>
   </fills>
   <borders count="2">
@@ -88,27 +178,24 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+  <cellXfs count="7">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -143,13 +230,25 @@
     <dxf>
       <fill>
         <patternFill>
-          <bgColor theme="3" tint="0.5999633777886288"/>
+          <bgColor theme="3" tint="0.59996337778862885"/>
         </patternFill>
       </fill>
     </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <colors/>
+  <colors>
+    <mruColors>
+      <color rgb="FFFF6565"/>
+    </mruColors>
+  </colors>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -437,281 +536,176 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:H6"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col width="15" customWidth="1" min="2" max="2"/>
-    <col width="48" customWidth="1" min="3" max="3"/>
-    <col width="41.5703125" customWidth="1" min="4" max="4"/>
-    <col width="33.42578125" customWidth="1" min="5" max="6"/>
-    <col width="91.42578125" bestFit="1" customWidth="1" min="8" max="8"/>
+    <col min="2" max="2" width="15" customWidth="1"/>
+    <col min="3" max="3" width="48" customWidth="1"/>
+    <col min="4" max="4" width="41.5703125" customWidth="1"/>
+    <col min="5" max="6" width="33.42578125" customWidth="1"/>
+    <col min="8" max="8" width="91.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Num</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>ID</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Summary</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>Pasos</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>Expected Result</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>Obtained Result</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>Status</t>
-        </is>
-      </c>
-      <c r="H1" s="2" t="inlineStr">
-        <is>
-          <t>Notes</t>
-        </is>
+    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="2" t="s">
+        <v>7</v>
       </c>
     </row>
-    <row r="2" ht="30" customFormat="1" customHeight="1" s="5">
-      <c r="A2" s="4" t="n">
+    <row r="2" spans="1:8" s="5" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+      <c r="A2" s="4">
         <v>1</v>
       </c>
-      <c r="B2" s="4" t="inlineStr">
-        <is>
-          <t>HISCLO001</t>
-        </is>
-      </c>
-      <c r="C2" s="4" t="inlineStr">
-        <is>
-          <t>closure page home</t>
-        </is>
-      </c>
-      <c r="D2" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1. The users clicks "Cierres"
-</t>
-        </is>
-      </c>
-      <c r="E2" s="3" t="inlineStr">
-        <is>
-          <t>1. Closure page home is correctly.</t>
-        </is>
-      </c>
-      <c r="F2" s="3" t="inlineStr">
-        <is>
-          <t>Closures page home works correctly.</t>
-        </is>
-      </c>
-      <c r="G2" s="7" t="inlineStr">
-        <is>
-          <t>FIXED</t>
-        </is>
-      </c>
-      <c r="H2" s="3" t="inlineStr">
-        <is>
-          <t>Fixed: ClosureDetailModal was referencing taxConfig variable that was not in its scope (separate function, not nested). Added taxConfig as a prop to fix the ReferenceError that crashed the page. Also added .filtersRow CSS class that was missing, causing broken layout.</t>
-        </is>
+      <c r="B2" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="C2" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F2" s="3"/>
+      <c r="G2" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="H2" s="3" t="s">
+        <v>25</v>
       </c>
     </row>
-    <row r="3" ht="30" customFormat="1" customHeight="1" s="5">
-      <c r="A3" s="4" t="n">
+    <row r="3" spans="1:8" s="5" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+      <c r="A3" s="4">
         <v>2</v>
       </c>
-      <c r="B3" s="4" t="inlineStr">
-        <is>
-          <t>HISCLO002</t>
-        </is>
-      </c>
-      <c r="C3" s="4" t="inlineStr">
-        <is>
-          <t>Closure between dates</t>
-        </is>
-      </c>
-      <c r="D3" s="3" t="inlineStr">
-        <is>
-          <t>1. The user selects "desde"
-2. The user selects "hasta"</t>
-        </is>
-      </c>
-      <c r="E3" s="3" t="inlineStr">
-        <is>
-          <t>1. Closure are shown.</t>
-        </is>
-      </c>
-      <c r="F3" s="3" t="inlineStr">
-        <is>
-          <t>Filter by date works.</t>
-        </is>
-      </c>
-      <c r="G3" s="7" t="inlineStr">
-        <is>
-          <t>FIXED</t>
-        </is>
-      </c>
-      <c r="H3" s="3" t="inlineStr">
-        <is>
-          <t>Fixed as part of HISCLO001.</t>
-        </is>
+      <c r="B3" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="E3" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="F3" s="3"/>
+      <c r="G3" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="H3" s="3" t="s">
+        <v>25</v>
       </c>
     </row>
-    <row r="4" ht="45" customFormat="1" customHeight="1" s="5">
-      <c r="A4" s="4" t="n">
+    <row r="4" spans="1:8" s="5" customFormat="1" ht="45" x14ac:dyDescent="0.25">
+      <c r="A4" s="4">
         <v>3</v>
       </c>
-      <c r="B4" s="4" t="inlineStr">
-        <is>
-          <t>HISCLO003</t>
-        </is>
-      </c>
-      <c r="C4" s="4" t="inlineStr">
-        <is>
-          <t>Filter: Closure by type</t>
-        </is>
-      </c>
-      <c r="D4" s="3" t="inlineStr">
-        <is>
-          <t>1. The user selects "desde"
-2. The user selects "hasta"
-3. The user selects type.</t>
-        </is>
-      </c>
-      <c r="E4" s="3" t="inlineStr">
-        <is>
-          <t>1. Closure are shown.</t>
-        </is>
-      </c>
-      <c r="F4" s="3" t="inlineStr">
-        <is>
-          <t>Filter by closure type works.</t>
-        </is>
-      </c>
-      <c r="G4" s="7" t="inlineStr">
-        <is>
-          <t>FIXED</t>
-        </is>
-      </c>
-      <c r="H4" s="3" t="inlineStr">
-        <is>
-          <t>Fixed as part of HISCLO001.</t>
-        </is>
+      <c r="B4" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="E4" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="F4" s="3"/>
+      <c r="G4" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="H4" s="3" t="s">
+        <v>25</v>
       </c>
     </row>
-    <row r="5" ht="45" customFormat="1" customHeight="1" s="5">
-      <c r="A5" s="4" t="n">
+    <row r="5" spans="1:8" s="5" customFormat="1" ht="45" x14ac:dyDescent="0.25">
+      <c r="A5" s="4">
         <v>4</v>
       </c>
-      <c r="B5" s="4" t="inlineStr">
-        <is>
-          <t>HISCLO004</t>
-        </is>
-      </c>
-      <c r="C5" s="4" t="inlineStr">
-        <is>
-          <t>Filter: Closure by waiter</t>
-        </is>
-      </c>
-      <c r="D5" s="3" t="inlineStr">
-        <is>
-          <t>1. The user selects "desde"
-2. The user selects "hasta"
-3. The user selects waiter.</t>
-        </is>
-      </c>
-      <c r="E5" s="3" t="inlineStr">
-        <is>
-          <t>1. Closure are shown.</t>
-        </is>
-      </c>
-      <c r="F5" s="3" t="inlineStr">
-        <is>
-          <t>Filter by waiter works.</t>
-        </is>
-      </c>
-      <c r="G5" s="7" t="inlineStr">
-        <is>
-          <t>FIXED</t>
-        </is>
-      </c>
-      <c r="H5" s="3" t="inlineStr">
-        <is>
-          <t>Fixed as part of HISCLO001.</t>
-        </is>
+      <c r="B5" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="C5" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="D5" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="E5" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="F5" s="3"/>
+      <c r="G5" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="H5" s="3" t="s">
+        <v>25</v>
       </c>
     </row>
-    <row r="6" customFormat="1" s="5">
-      <c r="A6" s="4" t="n">
+    <row r="6" spans="1:8" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="4">
         <v>5</v>
       </c>
-      <c r="B6" s="4" t="inlineStr">
-        <is>
-          <t>HISCLO005</t>
-        </is>
-      </c>
-      <c r="C6" s="5" t="inlineStr">
-        <is>
-          <t>Filter: clean</t>
-        </is>
-      </c>
-      <c r="D6" s="3" t="inlineStr">
-        <is>
-          <t>1. The user clicks "Limpiar fitros"</t>
-        </is>
-      </c>
-      <c r="E6" s="3" t="inlineStr">
-        <is>
-          <t>1. There is not a filter</t>
-        </is>
-      </c>
-      <c r="F6" s="3" t="inlineStr">
-        <is>
-          <t>Clear filters works.</t>
-        </is>
-      </c>
-      <c r="G6" s="7" t="inlineStr">
-        <is>
-          <t>FIXED</t>
-        </is>
-      </c>
-      <c r="H6" s="3" t="inlineStr">
-        <is>
-          <t>Fixed as part of HISCLO001.</t>
-        </is>
+      <c r="B6" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="C6" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="E6" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="F6" s="3"/>
+      <c r="G6" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="H6" s="3" t="s">
+        <v>25</v>
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="3" type="noConversion"/>
   <conditionalFormatting sqref="G2:G6">
-    <cfRule type="containsText" priority="1" operator="containsText" dxfId="3" text="PTE">
+    <cfRule type="containsText" dxfId="3" priority="1" operator="containsText" text="PTE">
       <formula>NOT(ISERROR(SEARCH("PTE",G2)))</formula>
     </cfRule>
-    <cfRule type="containsText" priority="2" operator="containsText" dxfId="2" text="BL">
+    <cfRule type="containsText" dxfId="2" priority="2" operator="containsText" text="BL">
       <formula>NOT(ISERROR(SEARCH("BL",G2)))</formula>
     </cfRule>
-    <cfRule type="containsText" priority="3" operator="containsText" dxfId="1" text="KO">
+    <cfRule type="containsText" dxfId="1" priority="3" operator="containsText" text="KO">
       <formula>NOT(ISERROR(SEARCH("KO",G2)))</formula>
     </cfRule>
-    <cfRule type="containsText" priority="4" operator="containsText" dxfId="0" text="OK">
+    <cfRule type="containsText" dxfId="0" priority="4" operator="containsText" text="OK">
       <formula>NOT(ISERROR(SEARCH("OK",G2)))</formula>
     </cfRule>
   </conditionalFormatting>

--- a/Web/TestCasesWeb/Cierres.xlsx
+++ b/Web/TestCasesWeb/Cierres.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Nerea QA\PycharmProjects\KOVAI\Web\TestCases\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Nerea QA\PycharmProjects\KOVAI\Web\TestCasesWeb\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{11B79476-3A2B-4A71-BDBC-D92805E4F2AE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B57DC17F-CE12-4572-8DE0-77CA6A7194B1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="630" yWindow="735" windowWidth="27795" windowHeight="14865" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="28">
   <si>
     <t>Num</t>
   </si>
@@ -98,18 +98,20 @@
     <t>1. The user clicks "Limpiar fitros"</t>
   </si>
   <si>
-    <t>BL</t>
-  </si>
-  <si>
-    <t>No se puede seleccionar nada</t>
-  </si>
-  <si>
     <t>Filter: Closure by type</t>
   </si>
   <si>
     <t>1. The user selects "desde"
 2. The user selects "hasta"
 3. The user selects type.</t>
+  </si>
+  <si>
+    <t>No se puede seleccionar nada
+15/04/26: Fixed as part of HISCLO001.</t>
+  </si>
+  <si>
+    <t>No se puede seleccionar nada
+15/04/26: Fixed: ClosureDetailModal was referencing taxConfig variable that was not in its scope (separate function, not nested). Added taxConfig as a prop to fix the ReferenceError that crashed the page. Also added .filtersRow CSS class that was missing, causing broken layout.</t>
   </si>
 </sst>
 </file>
@@ -573,7 +575,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:8" s="5" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:8" s="5" customFormat="1" ht="60" x14ac:dyDescent="0.25">
       <c r="A2" s="4">
         <v>1</v>
       </c>
@@ -590,11 +592,9 @@
         <v>10</v>
       </c>
       <c r="F2" s="3"/>
-      <c r="G2" s="6" t="s">
-        <v>24</v>
-      </c>
+      <c r="G2" s="6"/>
       <c r="H2" s="3" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
     </row>
     <row r="3" spans="1:8" s="5" customFormat="1" ht="30" x14ac:dyDescent="0.25">
@@ -614,11 +614,9 @@
         <v>19</v>
       </c>
       <c r="F3" s="3"/>
-      <c r="G3" s="6" t="s">
-        <v>24</v>
-      </c>
+      <c r="G3" s="6"/>
       <c r="H3" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="4" spans="1:8" s="5" customFormat="1" ht="45" x14ac:dyDescent="0.25">
@@ -629,20 +627,18 @@
         <v>15</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="E4" s="3" t="s">
         <v>19</v>
       </c>
       <c r="F4" s="3"/>
-      <c r="G4" s="6" t="s">
-        <v>24</v>
-      </c>
+      <c r="G4" s="6"/>
       <c r="H4" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="5" spans="1:8" s="5" customFormat="1" ht="45" x14ac:dyDescent="0.25">
@@ -662,14 +658,12 @@
         <v>19</v>
       </c>
       <c r="F5" s="3"/>
-      <c r="G5" s="6" t="s">
-        <v>24</v>
-      </c>
+      <c r="G5" s="6"/>
       <c r="H5" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
-    <row r="6" spans="1:8" s="5" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:8" s="5" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A6" s="4">
         <v>5</v>
       </c>
@@ -686,11 +680,9 @@
         <v>20</v>
       </c>
       <c r="F6" s="3"/>
-      <c r="G6" s="6" t="s">
-        <v>24</v>
-      </c>
+      <c r="G6" s="6"/>
       <c r="H6" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
   </sheetData>

--- a/Web/TestCasesWeb/Cierres.xlsx
+++ b/Web/TestCasesWeb/Cierres.xlsx
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B57DC17F-CE12-4572-8DE0-77CA6A7194B1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="630" yWindow="735" windowWidth="27795" windowHeight="14865" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>

--- a/Web/TestCasesWeb/Cierres.xlsx
+++ b/Web/TestCasesWeb/Cierres.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Nerea QA\PycharmProjects\KOVAI\Web\TestCasesWeb\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B57DC17F-CE12-4572-8DE0-77CA6A7194B1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{83E1E5D7-63FE-4CC6-9A75-1D9045AE079D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1005" yWindow="615" windowWidth="27795" windowHeight="14865" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="29">
   <si>
     <t>Num</t>
   </si>
@@ -106,19 +106,48 @@
 3. The user selects type.</t>
   </si>
   <si>
-    <t>No se puede seleccionar nada
-15/04/26: Fixed as part of HISCLO001.</t>
-  </si>
-  <si>
-    <t>No se puede seleccionar nada
-15/04/26: Fixed: ClosureDetailModal was referencing taxConfig variable that was not in its scope (separate function, not nested). Added taxConfig as a prop to fix the ReferenceError that crashed the page. Also added .filtersRow CSS class that was missing, causing broken layout.</t>
+    <r>
+      <t xml:space="preserve">No se puede seleccionar nada
+15/04/26: Fixed: ClosureDetailModal was referencing taxConfig variable that was not in its scope (separate function, not nested). Added taxConfig as a prop to fix the ReferenceError that crashed the page. Also added .filtersRow CSS class that was missing, causing broken layout.
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>17/04/26: No se puede seleccionar nada</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">No se puede seleccionar nada
+15/04/26: Fixed as part of HISCLO001.
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>17/04/26: No se puede seleccionar nada</t>
+    </r>
+  </si>
+  <si>
+    <t>KO</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -140,6 +169,13 @@
     </font>
     <font>
       <sz val="8"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -575,7 +611,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:8" s="5" customFormat="1" ht="60" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:8" s="5" customFormat="1" ht="75" x14ac:dyDescent="0.25">
       <c r="A2" s="4">
         <v>1</v>
       </c>
@@ -592,12 +628,14 @@
         <v>10</v>
       </c>
       <c r="F2" s="3"/>
-      <c r="G2" s="6"/>
+      <c r="G2" s="6" t="s">
+        <v>28</v>
+      </c>
       <c r="H2" s="3" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
-    <row r="3" spans="1:8" s="5" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:8" s="5" customFormat="1" ht="45" x14ac:dyDescent="0.25">
       <c r="A3" s="4">
         <v>2</v>
       </c>
@@ -614,9 +652,11 @@
         <v>19</v>
       </c>
       <c r="F3" s="3"/>
-      <c r="G3" s="6"/>
+      <c r="G3" s="6" t="s">
+        <v>28</v>
+      </c>
       <c r="H3" s="3" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="4" spans="1:8" s="5" customFormat="1" ht="45" x14ac:dyDescent="0.25">
@@ -636,9 +676,11 @@
         <v>19</v>
       </c>
       <c r="F4" s="3"/>
-      <c r="G4" s="6"/>
+      <c r="G4" s="6" t="s">
+        <v>28</v>
+      </c>
       <c r="H4" s="3" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="5" spans="1:8" s="5" customFormat="1" ht="45" x14ac:dyDescent="0.25">
@@ -658,12 +700,14 @@
         <v>19</v>
       </c>
       <c r="F5" s="3"/>
-      <c r="G5" s="6"/>
+      <c r="G5" s="6" t="s">
+        <v>28</v>
+      </c>
       <c r="H5" s="3" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
-    <row r="6" spans="1:8" s="5" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:8" s="5" customFormat="1" ht="45" x14ac:dyDescent="0.25">
       <c r="A6" s="4">
         <v>5</v>
       </c>
@@ -680,9 +724,11 @@
         <v>20</v>
       </c>
       <c r="F6" s="3"/>
-      <c r="G6" s="6"/>
+      <c r="G6" s="6" t="s">
+        <v>28</v>
+      </c>
       <c r="H6" s="3" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
   </sheetData>
@@ -702,5 +748,6 @@
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
--- a/Web/TestCasesWeb/Cierres.xlsx
+++ b/Web/TestCasesWeb/Cierres.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Nerea QA\PycharmProjects\KOVAI\Web\TestCasesWeb\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{83E1E5D7-63FE-4CC6-9A75-1D9045AE079D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DCC3CBB6-8D53-445C-AAC9-289C229C6ED0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1005" yWindow="615" windowWidth="27795" windowHeight="14865" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43" uniqueCount="29">
   <si>
     <t>Num</t>
   </si>
@@ -44,21 +44,6 @@
   </si>
   <si>
     <t>Notes</t>
-  </si>
-  <si>
-    <t>Filter: clean</t>
-  </si>
-  <si>
-    <t>closure page home</t>
-  </si>
-  <si>
-    <t>1. Closure page home is correctly.</t>
-  </si>
-  <si>
-    <t>Closure between dates</t>
-  </si>
-  <si>
-    <t>Filter: Closure by waiter</t>
   </si>
   <si>
     <t>HISCLO001</t>
@@ -98,49 +83,42 @@
     <t>1. The user clicks "Limpiar fitros"</t>
   </si>
   <si>
-    <t>Filter: Closure by type</t>
-  </si>
-  <si>
     <t>1. The user selects "desde"
 2. The user selects "hasta"
 3. The user selects type.</t>
   </si>
   <si>
-    <r>
-      <t xml:space="preserve">No se puede seleccionar nada
+    <t>1. Closure page  is correctly.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Closure page </t>
+  </si>
+  <si>
+    <t>Closure: between dates</t>
+  </si>
+  <si>
+    <t>Closure: Filter by type</t>
+  </si>
+  <si>
+    <t>Closure: Filter by waiter</t>
+  </si>
+  <si>
+    <t>Closure: Filter, clean</t>
+  </si>
+  <si>
+    <t>OK</t>
+  </si>
+  <si>
+    <t>No se puede seleccionar nada
 15/04/26: Fixed: ClosureDetailModal was referencing taxConfig variable that was not in its scope (separate function, not nested). Added taxConfig as a prop to fix the ReferenceError that crashed the page. Also added .filtersRow CSS class that was missing, causing broken layout.
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>17/04/26: No se puede seleccionar nada</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">No se puede seleccionar nada
+17/04/26: No se puede seleccionar nada
+18/05/26: Se ven ya cierres</t>
+  </si>
+  <si>
+    <t>No se puede seleccionar nada
 15/04/26: Fixed as part of HISCLO001.
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>17/04/26: No se puede seleccionar nada</t>
-    </r>
-  </si>
-  <si>
-    <t>KO</t>
+17/04/26: No se puede seleccionar nada
+18/05/26: Se ven ya cierres</t>
   </si>
 </sst>
 </file>
@@ -175,7 +153,6 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FFFF0000"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -216,7 +193,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
@@ -235,6 +212,9 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -611,124 +591,134 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:8" s="5" customFormat="1" ht="75" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:8" s="5" customFormat="1" ht="90" x14ac:dyDescent="0.25">
       <c r="A2" s="4">
         <v>1</v>
       </c>
       <c r="B2" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="C2" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="D2" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="C2" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="D2" s="3" t="s">
-        <v>18</v>
-      </c>
       <c r="E2" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="F2" s="3"/>
+        <v>20</v>
+      </c>
+      <c r="F2" s="3" t="s">
+        <v>20</v>
+      </c>
       <c r="G2" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="H2" s="3" t="s">
         <v>26</v>
       </c>
+      <c r="H2" s="7" t="s">
+        <v>27</v>
+      </c>
     </row>
-    <row r="3" spans="1:8" s="5" customFormat="1" ht="45" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:8" s="5" customFormat="1" ht="60" x14ac:dyDescent="0.25">
       <c r="A3" s="4">
         <v>2</v>
       </c>
       <c r="B3" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E3" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="C3" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="D3" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="E3" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="F3" s="3"/>
+      <c r="F3" s="3" t="s">
+        <v>14</v>
+      </c>
       <c r="G3" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="H3" s="7" t="s">
         <v>28</v>
       </c>
-      <c r="H3" s="3" t="s">
-        <v>27</v>
-      </c>
     </row>
-    <row r="4" spans="1:8" s="5" customFormat="1" ht="45" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:8" s="5" customFormat="1" ht="60" x14ac:dyDescent="0.25">
       <c r="A4" s="4">
         <v>3</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="F4" s="3"/>
+        <v>14</v>
+      </c>
+      <c r="F4" s="3" t="s">
+        <v>14</v>
+      </c>
       <c r="G4" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="H4" s="7" t="s">
         <v>28</v>
       </c>
-      <c r="H4" s="3" t="s">
-        <v>27</v>
-      </c>
     </row>
-    <row r="5" spans="1:8" s="5" customFormat="1" ht="45" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:8" s="5" customFormat="1" ht="60" x14ac:dyDescent="0.25">
       <c r="A5" s="4">
         <v>4</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="F5" s="3"/>
+        <v>14</v>
+      </c>
+      <c r="F5" s="3" t="s">
+        <v>14</v>
+      </c>
       <c r="G5" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="H5" s="7" t="s">
         <v>28</v>
       </c>
-      <c r="H5" s="3" t="s">
-        <v>27</v>
-      </c>
     </row>
-    <row r="6" spans="1:8" s="5" customFormat="1" ht="45" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:8" s="5" customFormat="1" ht="60" x14ac:dyDescent="0.25">
       <c r="A6" s="4">
         <v>5</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="C6" s="5" t="s">
-        <v>8</v>
+        <v>12</v>
+      </c>
+      <c r="C6" s="4" t="s">
+        <v>25</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="F6" s="3"/>
+        <v>15</v>
+      </c>
+      <c r="F6" s="3" t="s">
+        <v>15</v>
+      </c>
       <c r="G6" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="H6" s="7" t="s">
         <v>28</v>
-      </c>
-      <c r="H6" s="3" t="s">
-        <v>27</v>
       </c>
     </row>
   </sheetData>
